--- a/Collections/Kazakhstan/#Kazakhstan#Commercial#[2004-present]#circulation_quality.xlsx
+++ b/Collections/Kazakhstan/#Kazakhstan#Commercial#[2004-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Kazakhstan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5903C32B-0013-4C87-B2F1-662425C9E5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5261A880-B6F8-4F57-AEEA-A72046345C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="33150" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="100тенге" sheetId="25" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -77,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="120">
   <si>
     <t>-</t>
   </si>
@@ -410,6 +413,33 @@
   </si>
   <si>
     <t>Subtype_2#Composition</t>
+  </si>
+  <si>
+    <t>Wildlife of Kazakhstan</t>
+  </si>
+  <si>
+    <t>30th Anniversary - Constitution of Kazakhstan</t>
+  </si>
+  <si>
+    <t>5.000.000</t>
+  </si>
+  <si>
+    <t>3.000.000</t>
+  </si>
+  <si>
+    <t>Snow Leopard</t>
+  </si>
+  <si>
+    <t>Saiga Antelope</t>
+  </si>
+  <si>
+    <t>Great Bustard</t>
+  </si>
+  <si>
+    <t>Falcon</t>
+  </si>
+  <si>
+    <t>Argali</t>
   </si>
 </sst>
 </file>
@@ -659,7 +689,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -725,6 +755,9 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -741,7 +774,63 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="70">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
@@ -1252,9 +1341,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="8" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1557,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F9C7DAA-01C4-4861-B3EA-F5AF89B42AE1}">
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -1569,14 +1658,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="20"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
@@ -1585,7 +1674,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
+      <c r="A2" s="25"/>
       <c r="B2" s="21" t="s">
         <v>14</v>
       </c>
@@ -3635,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="10" t="str">
-        <f t="shared" ref="G89:G92" si="17">IF(OR(AND(F89&gt;1,F89&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G89:G99" si="17">IF(OR(AND(F89&gt;1,F89&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3705,10 +3794,171 @@
         <v/>
       </c>
     </row>
+    <row r="93" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="23">
+        <v>2024</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G93" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
     <row r="94" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B94"/>
-      <c r="F94" s="1"/>
-      <c r="G94"/>
+      <c r="A94" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0</v>
+      </c>
+      <c r="G94" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B95" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B97" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B98" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="23">
+        <v>2025</v>
+      </c>
+      <c r="B99" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{1F9C7DAA-01C4-4861-B3EA-F5AF89B42AE1}"/>
@@ -3718,7 +3968,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F5:F11 F17 F19:F28 F39">
-    <cfRule type="colorScale" priority="190">
+    <cfRule type="colorScale" priority="204">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3730,11 +3980,759 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F11 F17 F19:F28 F39">
-    <cfRule type="containsText" dxfId="62" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="203" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F77 F67 F79 F89 F91">
+  <conditionalFormatting sqref="F67 F77 F79 F89 F91">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F67 F77 F79 F89 F91">
+    <cfRule type="containsText" dxfId="68" priority="81" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F67))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="196">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="67" priority="195" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="182">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="containsText" dxfId="66" priority="181" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
+    <cfRule type="colorScale" priority="122">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
+    <cfRule type="containsText" dxfId="65" priority="121" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="colorScale" priority="152">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="containsText" dxfId="64" priority="151" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="colorScale" priority="154">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="containsText" dxfId="63" priority="153" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37">
+    <cfRule type="colorScale" priority="114">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37">
+    <cfRule type="containsText" dxfId="62" priority="113" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F37))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F30">
+    <cfRule type="colorScale" priority="128">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F30">
+    <cfRule type="containsText" dxfId="61" priority="127" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="colorScale" priority="126">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="containsText" dxfId="60" priority="125" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F82 F80 F84">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F80 F82 F84">
+    <cfRule type="containsText" dxfId="59" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F80))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="colorScale" priority="150">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="containsText" dxfId="58" priority="149" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="colorScale" priority="148">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="containsText" dxfId="57" priority="147" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="colorScale" priority="132">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="56" priority="131" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="colorScale" priority="140">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="55" priority="139" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F70">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F70">
+    <cfRule type="containsText" dxfId="54" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F70))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32">
+    <cfRule type="colorScale" priority="124">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32">
+    <cfRule type="containsText" dxfId="53" priority="123" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36">
+    <cfRule type="colorScale" priority="116">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36">
+    <cfRule type="containsText" dxfId="52" priority="115" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F36))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="colorScale" priority="120">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="containsText" dxfId="51" priority="119" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F38">
+    <cfRule type="colorScale" priority="112">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F38">
+    <cfRule type="containsText" dxfId="50" priority="111" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F38))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F81 F83">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F81 F83">
+    <cfRule type="containsText" dxfId="49" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F81))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F71">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F71">
+    <cfRule type="containsText" dxfId="48" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F71))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F76">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F76">
+    <cfRule type="containsText" dxfId="47" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F76))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F40:F41">
+    <cfRule type="colorScale" priority="106">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F40:F41">
+    <cfRule type="containsText" dxfId="46" priority="105" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F40))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F42">
+    <cfRule type="colorScale" priority="104">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F42">
+    <cfRule type="containsText" dxfId="45" priority="103" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F42))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35">
+    <cfRule type="colorScale" priority="118">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35">
+    <cfRule type="containsText" dxfId="44" priority="117" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F86">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F86">
+    <cfRule type="containsText" dxfId="43" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F86))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F87">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F87">
+    <cfRule type="containsText" dxfId="42" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F87))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F88">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F88">
+    <cfRule type="containsText" dxfId="41" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F88))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43">
+    <cfRule type="colorScale" priority="110">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43">
+    <cfRule type="containsText" dxfId="40" priority="109" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F43))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F44">
+    <cfRule type="colorScale" priority="102">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F44">
+    <cfRule type="containsText" dxfId="39" priority="101" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F44))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F45:F46">
+    <cfRule type="colorScale" priority="98">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F45:F46">
+    <cfRule type="containsText" dxfId="38" priority="97" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F45))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47">
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47">
+    <cfRule type="containsText" dxfId="37" priority="95" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F47))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F48">
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F48">
+    <cfRule type="containsText" dxfId="36" priority="93" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F48))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F49">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F49">
+    <cfRule type="containsText" dxfId="35" priority="91" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F49))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F50">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F50">
+    <cfRule type="containsText" dxfId="34" priority="89" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F50))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F63">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F63">
+    <cfRule type="containsText" dxfId="33" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F63))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F51">
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F51">
+    <cfRule type="containsText" dxfId="32" priority="85" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F51))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F68">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F68">
+    <cfRule type="containsText" dxfId="31" priority="83" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F68))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F52">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F52">
+    <cfRule type="containsText" dxfId="30" priority="79" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F52))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F53">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F53">
+    <cfRule type="containsText" dxfId="29" priority="77" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F53))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F54">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F54">
+    <cfRule type="containsText" dxfId="28" priority="75" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F54))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F55">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F55">
+    <cfRule type="containsText" dxfId="27" priority="73" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F55))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F56">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F56">
+    <cfRule type="containsText" dxfId="26" priority="71" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F56))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F57">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F57">
+    <cfRule type="containsText" dxfId="25" priority="69" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F57))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F58">
     <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3746,148 +4744,267 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F67 F77 F79 F89 F91">
-    <cfRule type="containsText" dxfId="61" priority="67" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F67))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="colorScale" priority="182">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="containsText" dxfId="60" priority="181" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="colorScale" priority="168">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="59" priority="167" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
-    <cfRule type="colorScale" priority="108">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
-    <cfRule type="containsText" dxfId="58" priority="107" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="colorScale" priority="138">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="containsText" dxfId="57" priority="137" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="colorScale" priority="140">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="56" priority="139" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
-    <cfRule type="colorScale" priority="100">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
-    <cfRule type="containsText" dxfId="55" priority="99" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F37))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F30">
-    <cfRule type="colorScale" priority="114">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F30">
-    <cfRule type="containsText" dxfId="54" priority="113" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
-    <cfRule type="colorScale" priority="112">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
-    <cfRule type="containsText" dxfId="53" priority="111" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F80 F82 F84">
+  <conditionalFormatting sqref="F58">
+    <cfRule type="containsText" dxfId="24" priority="67" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F58))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F59">
+    <cfRule type="containsText" dxfId="23" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F59))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F60">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F60">
+    <cfRule type="containsText" dxfId="22" priority="61" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F60))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F61">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F61">
+    <cfRule type="containsText" dxfId="21" priority="59" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F61))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F62">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F62">
+    <cfRule type="containsText" dxfId="20" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F62))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F64">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F64">
+    <cfRule type="containsText" dxfId="19" priority="51" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F64))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F65">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F65">
+    <cfRule type="containsText" dxfId="18" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F65))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F66">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F66">
+    <cfRule type="containsText" dxfId="17" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F66))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F78 F90 F92">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F78 F90 F92">
+    <cfRule type="containsText" dxfId="16" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F78))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69">
+    <cfRule type="containsText" dxfId="15" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F69))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F72">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F72">
+    <cfRule type="containsText" dxfId="14" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F72))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F73">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F73">
+    <cfRule type="containsText" dxfId="13" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F73))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F74">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F74">
+    <cfRule type="containsText" dxfId="12" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F74))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F75">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F75">
+    <cfRule type="containsText" dxfId="11" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F75))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F85">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F85">
+    <cfRule type="containsText" dxfId="10" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F85))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F93">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F93">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F93))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F95">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3899,165 +5016,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F80 F82 F84">
-    <cfRule type="containsText" dxfId="52" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F80))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="colorScale" priority="136">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="51" priority="135" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="colorScale" priority="134">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="50" priority="133" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="colorScale" priority="118">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="containsText" dxfId="49" priority="117" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="colorScale" priority="126">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="48" priority="125" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F70">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F70">
-    <cfRule type="containsText" dxfId="47" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F70))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="colorScale" priority="110">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="containsText" dxfId="46" priority="109" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
-    <cfRule type="colorScale" priority="102">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
-    <cfRule type="containsText" dxfId="45" priority="101" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F36))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="colorScale" priority="106">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="containsText" dxfId="44" priority="105" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
-    <cfRule type="colorScale" priority="98">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
-    <cfRule type="containsText" dxfId="43" priority="97" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F38))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F83 F81">
+  <conditionalFormatting sqref="F95">
+    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F95))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F94">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4069,97 +5033,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F81 F83">
-    <cfRule type="containsText" dxfId="42" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F81))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F71">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F71">
-    <cfRule type="containsText" dxfId="41" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F71))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F76">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F76">
-    <cfRule type="containsText" dxfId="40" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F76))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F40:F41">
-    <cfRule type="colorScale" priority="92">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F40:F41">
-    <cfRule type="containsText" dxfId="39" priority="91" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F40))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F42">
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F42">
-    <cfRule type="containsText" dxfId="38" priority="89" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F42))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F35">
-    <cfRule type="colorScale" priority="104">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F35">
-    <cfRule type="containsText" dxfId="37" priority="103" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F86">
+  <conditionalFormatting sqref="F94">
+    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F94))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F96">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F96">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F96))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F98">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4171,12 +5067,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F86">
-    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F86))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F87">
+  <conditionalFormatting sqref="F98">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F98))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F97">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4188,12 +5084,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F87">
-    <cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F87))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F88">
+  <conditionalFormatting sqref="F97">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F97))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F99">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4205,536 +5101,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F88">
-    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F88))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43">
-    <cfRule type="colorScale" priority="96">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43">
-    <cfRule type="containsText" dxfId="33" priority="95" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F44">
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F44">
-    <cfRule type="containsText" dxfId="32" priority="87" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F44))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F45:F46">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F45:F46">
-    <cfRule type="containsText" dxfId="31" priority="83" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F45))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F47">
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F47">
-    <cfRule type="containsText" dxfId="30" priority="81" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F47))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F48">
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F48">
-    <cfRule type="containsText" dxfId="29" priority="79" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F48))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F49">
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F49">
-    <cfRule type="containsText" dxfId="28" priority="77" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F49))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F50">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F50">
-    <cfRule type="containsText" dxfId="27" priority="75" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F50))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F63">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F63">
-    <cfRule type="containsText" dxfId="26" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F63))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F51">
-    <cfRule type="colorScale" priority="72">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F51">
-    <cfRule type="containsText" dxfId="25" priority="71" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F51))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F68">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F68">
-    <cfRule type="containsText" dxfId="24" priority="69" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F68))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F52">
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F52">
-    <cfRule type="containsText" dxfId="23" priority="65" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F52))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F53">
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F53">
-    <cfRule type="containsText" dxfId="22" priority="63" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F53))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F54">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F54">
-    <cfRule type="containsText" dxfId="21" priority="61" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F54))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F55">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F55">
-    <cfRule type="containsText" dxfId="20" priority="59" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F55))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F56">
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F56">
-    <cfRule type="containsText" dxfId="19" priority="57" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F56))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F57">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F57">
-    <cfRule type="containsText" dxfId="18" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F57))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F58">
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F58">
-    <cfRule type="containsText" dxfId="17" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F58))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F59">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F59">
-    <cfRule type="containsText" dxfId="16" priority="49" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F59))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F60">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F60">
-    <cfRule type="containsText" dxfId="15" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F60))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F61">
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F61">
-    <cfRule type="containsText" dxfId="14" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F61))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F62">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F62">
-    <cfRule type="containsText" dxfId="13" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F62))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F64">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F64">
-    <cfRule type="containsText" dxfId="12" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F64))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F65">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F65">
-    <cfRule type="containsText" dxfId="11" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F65))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F66">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F66">
-    <cfRule type="containsText" dxfId="10" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F66))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F90 F78 F92">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F78 F90 F92">
-    <cfRule type="containsText" dxfId="9" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F78))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69">
-    <cfRule type="containsText" dxfId="8" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F69))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F72">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F72">
-    <cfRule type="containsText" dxfId="7" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F72))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F73">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F73">
-    <cfRule type="containsText" dxfId="6" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F73))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F74">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F74">
-    <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F74))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F75">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F75">
-    <cfRule type="containsText" dxfId="4" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F75))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F85">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F85">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F85))))</formula>
+  <conditionalFormatting sqref="F99">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F99))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
